--- a/StructureDefinition-tk-provenance.xlsx
+++ b/StructureDefinition-tk-provenance.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1405" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1405" uniqueCount="331">
   <si>
     <t>Property</t>
   </si>
@@ -88,7 +88,9 @@
   </si>
   <si>
     <t>Spårbarhetspost för en registrering (skapande/uppdatering) av en eller flera
-resurser i tjänstekatalogen — vanligen skickad tillsammans med den/de
+resurser i tjänstekatalogen, inklusive administratörsbehörigheter
+([TKAdministratorRole](StructureDefinition-tk-administrator-role.html)) —
+vanligen skickad tillsammans med den/de
 registrerade resurserna i samma transaction-Bundle. Se
 [Kravkatalog](requirements.html) REQ-TRC-1/2 och "Distribution och
 synkronisering"/registrering i rest-interactions.html.</t>
@@ -502,7 +504,7 @@
     <t>Provenance.target</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.inera.se/ig/tjanstekatalog/StructureDefinition/tk-organization|https://fhir.inera.se/ig/tjanstekatalog/StructureDefinition/tk-endpoint|https://fhir.inera.se/ig/tjanstekatalog/StructureDefinition/tk-api-instance|https://fhir.inera.se/ig/tjanstekatalog/StructureDefinition/tk-api-specification-capability)
+    <t xml:space="preserve">Reference(https://fhir.inera.se/ig/tjanstekatalog/StructureDefinition/tk-organization|https://fhir.inera.se/ig/tjanstekatalog/StructureDefinition/tk-endpoint|https://fhir.inera.se/ig/tjanstekatalog/StructureDefinition/tk-api-instance|https://fhir.inera.se/ig/tjanstekatalog/StructureDefinition/tk-api-specification-capability|https://fhir.inera.se/ig/tjanstekatalog/StructureDefinition/tk-administrator-role)
 </t>
   </si>
   <si>
@@ -779,6 +781,9 @@
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 prov-1:Who and onBehalfOf cannot be the same {who.resolve().exists() and onBehalfOf.resolve().exists() implies who.resolve() != onBehalfOf.resolve()}prov-2:If who is a PractitionerRole, onBehalfOf can't reference the same Practitioner {who.resolve().ofType(PractitionerRole).practitioner.resolve().exists() and onBehalfOf.resolve().ofType(Practitioner).exists() implies who.resolve().practitioner.resolve() != onBehalfOf.resolve()}prov-3:If who is an organization, onBehalfOf can't be a PractitionerRole within that organization {who.resolve().ofType(Organization).exists() and onBehalfOf.resolve().ofType(PractitionerRole).organization.resolve().exists() implies who.resolve() != onBehalfOf.resolve().organization.resolve()}</t>
+  </si>
+  <si>
+    <t>REQ-TRC-1, REQ-TRC-3</t>
   </si>
   <si>
     <t>Event.performer</t>
@@ -1386,7 +1391,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="246.91796875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -3923,30 +3928,30 @@
         <v>242</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>158</v>
+        <v>243</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3969,13 +3974,13 @@
         <v>83</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4026,7 +4031,7 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4035,7 +4040,7 @@
         <v>94</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>83</v>
@@ -4050,7 +4055,7 @@
         <v>83</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>83</v>
@@ -4061,10 +4066,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4093,7 +4098,7 @@
         <v>143</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N23" t="s" s="2">
         <v>145</v>
@@ -4146,7 +4151,7 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -4170,7 +4175,7 @@
         <v>83</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>83</v>
@@ -4181,14 +4186,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4210,10 +4215,10 @@
         <v>142</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N24" t="s" s="2">
         <v>145</v>
@@ -4268,7 +4273,7 @@
         <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -4303,10 +4308,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4332,16 +4337,16 @@
         <v>211</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>83</v>
@@ -4369,10 +4374,10 @@
         <v>202</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>83</v>
@@ -4390,7 +4395,7 @@
         <v>83</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -4408,27 +4413,27 @@
         <v>83</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4454,16 +4459,16 @@
         <v>211</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>83</v>
@@ -4491,10 +4496,10 @@
         <v>202</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>83</v>
@@ -4512,7 +4517,7 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -4536,21 +4541,21 @@
         <v>83</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4573,13 +4578,13 @@
         <v>95</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4630,7 +4635,7 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>94</v>
@@ -4639,7 +4644,7 @@
         <v>94</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>106</v>
@@ -4648,13 +4653,13 @@
         <v>83</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>83</v>
@@ -4665,10 +4670,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4691,13 +4696,13 @@
         <v>83</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4748,7 +4753,7 @@
         <v>83</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -4757,7 +4762,7 @@
         <v>94</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>106</v>
@@ -4772,7 +4777,7 @@
         <v>83</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>83</v>
@@ -4783,10 +4788,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4812,10 +4817,10 @@
         <v>237</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4866,7 +4871,7 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -4890,21 +4895,21 @@
         <v>83</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4927,13 +4932,13 @@
         <v>83</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4984,7 +4989,7 @@
         <v>83</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -4993,7 +4998,7 @@
         <v>94</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>83</v>
@@ -5008,7 +5013,7 @@
         <v>83</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>83</v>
@@ -5019,10 +5024,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5051,7 +5056,7 @@
         <v>143</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N31" t="s" s="2">
         <v>145</v>
@@ -5104,7 +5109,7 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5128,7 +5133,7 @@
         <v>83</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>83</v>
@@ -5139,14 +5144,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5168,10 +5173,10 @@
         <v>142</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N32" t="s" s="2">
         <v>145</v>
@@ -5226,7 +5231,7 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5261,10 +5266,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5290,10 +5295,10 @@
         <v>114</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5323,10 +5328,10 @@
         <v>118</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>83</v>
@@ -5344,7 +5349,7 @@
         <v>83</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>94</v>
@@ -5368,21 +5373,21 @@
         <v>83</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5405,16 +5410,16 @@
         <v>95</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5464,7 +5469,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>94</v>
@@ -5488,7 +5493,7 @@
         <v>83</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>231</v>
@@ -5499,10 +5504,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5528,13 +5533,13 @@
         <v>84</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5584,7 +5589,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -5608,21 +5613,21 @@
         <v>83</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5645,13 +5650,13 @@
         <v>83</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5702,7 +5707,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -5726,7 +5731,7 @@
         <v>83</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>83</v>
